--- a/daily_matches/job_matches_2026-03-03.xlsx
+++ b/daily_matches/job_matches_2026-03-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sr Analyst, Risk Data Engineering</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Lincoln Financial Group</t>
+          <t>First Legal</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Radnor, PA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.9</v>
+        <v>11.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, Glue, Athena, Redshift, MLflow, CI/CD, Databricks, Redshift</t>
+          <t>AI Engineer, LangChain, RAG, Prompt Engineering, CI/CD, Git, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52bc5a9a6e784515</t>
+          <t>https://www.indeed.com/viewjob?jk=c3205766924fb90e</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Integration Platform</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>athenahealth</t>
+          <t>First Legal</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>White Plains, NY, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.6</v>
+        <v>11.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, EC2, Athena, Docker, Kubernetes, CI/CD, Terraform, Git, PostgreSQL, SQL</t>
+          <t>AI Engineer, LangChain, RAG, Prompt Engineering, CI/CD, Git, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,129 +531,129 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6ac2a746d527ccc</t>
+          <t>https://www.indeed.com/viewjob?jk=7724150631a274bb</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Dematic</t>
+          <t>First Legal</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.6</v>
+        <v>11.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, BigQuery, Data Lake, Dataflow, Docker, Kubernetes, CI/CD, Databricks, BigQuery</t>
+          <t>AI Engineer, LangChain, RAG, Prompt Engineering, CI/CD, Git, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9bde3d8a51e4f79</t>
+          <t>https://www.indeed.com/viewjob?jk=8dcf9c881b8b2b03</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Machine Learning Scientist I - Early Careers</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Wayfair</t>
+          <t>First Legal</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, Docker, CI/CD, Git, PySpark, Python, SQL, R</t>
+          <t>AI Engineer, LangChain, RAG, Prompt Engineering, CI/CD, Git, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6a21055f8c7bd5b</t>
+          <t>https://www.indeed.com/viewjob?jk=c893485b4c346aa0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>First Legal</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Berkeley Heights, NJ, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, CI/CD, Git, Snowflake, Tableau, Power BI, Python, SQL, R</t>
+          <t>AI Engineer, LangChain, RAG, Prompt Engineering, CI/CD, Git, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b50986d754294b4c</t>
+          <t>https://www.indeed.com/viewjob?jk=eccbf6b5fbbae8f0</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>First Legal</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Henderson, NV, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,34 +661,34 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, Git, PostgreSQL, Python, SQL, R, Java, Scala</t>
+          <t>AI Engineer, LangChain, RAG, Prompt Engineering, CI/CD, Git, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31b2c457ac06652a</t>
+          <t>https://www.indeed.com/viewjob?jk=1fed99ad6f10654d</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior AI/ML Architect, Applied Field Engineering</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>First Legal</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Henderson, NV, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,42 +696,42 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Prompt Engineering, PyTorch, Snowflake, Python, R</t>
+          <t>AI Engineer, LangChain, RAG, Prompt Engineering, CI/CD, Git, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b803ecb54348b17</t>
+          <t>https://www.indeed.com/viewjob?jk=4d0b466949a1bdb1</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software / AI Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>First Legal</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Hollywood, FL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, TensorFlow, PyTorch, FastAPI, Python, R, Scala, Optimization</t>
+          <t>AI Engineer, LangChain, RAG, Prompt Engineering, CI/CD, Git, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,147 +741,287 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4233fcbc0b17d245</t>
+          <t>https://www.indeed.com/viewjob?jk=9f4984cac15af1f8</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>E-Space</t>
+          <t>First Legal</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, FastAPI, Kafka, PostgreSQL, Python, SQL, R</t>
+          <t>AI Engineer, LangChain, RAG, Prompt Engineering, CI/CD, Git, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19f404beff844178</t>
+          <t>https://www.indeed.com/viewjob?jk=8f7dd33c1c8dd9ef</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>First Legal</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, PyTorch, Docker, Git, Python, R, Java</t>
+          <t>AI Engineer, LangChain, RAG, Prompt Engineering, CI/CD, Git, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31cc62ca31467b1d</t>
+          <t>https://www.indeed.com/viewjob?jk=c8b6a5f873843085</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Machine Learning Scientist II - Supplier Ads</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Wayfair</t>
+          <t>First Legal</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, XGBoost, MLflow, Docker, Kubernetes, Python, SQL, R, Scala</t>
+          <t>AI Engineer, LangChain, RAG, Prompt Engineering, CI/CD, Git, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1965482b714c1fcb</t>
+          <t>https://www.indeed.com/viewjob?jk=bd445525a9885001</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Software Engineer, AI Software Core (Multiple levels)</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>First Legal</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Paris, TN, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, Prompt Engineering, CI/CD, Git, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a8e2a2840837668d</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>GTM Engineer, Hazel AI</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>ALTRUIST</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>RAG, BigQuery, Snowflake, Databricks, BigQuery, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ace9e82efa6b4b13</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>GEN AI Engineer-1</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
         <v>10</v>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer, Generative AI, RAG, TensorFlow, PyTorch, Git, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, Prompt Engineering, Python, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f8c1f365e57c241d</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Marketing Analytics and Data Science Program Management Intern</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>AAA Life Insurance Company</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Livonia, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>10</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Data Scientist, Git, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
         <is>
           <t>2026-03-02</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a5ec1807b3a887e0</t>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=48646c7ec667696e</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Senior Product Software Engineer</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Wolters Kluwer</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>10</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, TensorFlow, PyTorch, Git, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f40684013e8a26dd</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-03-03.xlsx
+++ b/daily_matches/job_matches_2026-03-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Backend Software Engineer III - API Platform</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>First Legal</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>11.1</v>
+        <v>20</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, Prompt Engineering, CI/CD, Git, R, Java, Scala, Optimization</t>
+          <t>RAG, S3, Glue, Athena, Redshift, Docker, Kubernetes, Apache Airflow, Git, Snowflake</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3205766924fb90e</t>
+          <t>https://www.indeed.com/viewjob?jk=fd1c3ba542522bad</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>First Legal</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>White Plains, NY, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, Prompt Engineering, CI/CD, Git, R, Java, Scala, Optimization</t>
+          <t>Data Scientist, RAG, Dataflow, Kubernetes, CI/CD, Terraform, Git, Kafka, Python, SQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,94 +531,94 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7724150631a274bb</t>
+          <t>https://www.indeed.com/viewjob?jk=a53eba2ddb1389c4</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Senior Software Developer, Platform Engineering</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>First Legal</t>
+          <t>Redfin</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, Prompt Engineering, CI/CD, Git, R, Java, Scala, Optimization</t>
+          <t>RAG, Copilot, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8dcf9c881b8b2b03</t>
+          <t>https://www.indeed.com/viewjob?jk=44e5ced55abe02e5</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Software Development Engineer III - AI Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>First Legal</t>
+          <t>Expedia Group</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, Prompt Engineering, CI/CD, Git, R, Java, Scala, Optimization</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Gemini, Pinecone, CI/CD, Kafka, NoSQL, SQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c893485b4c346aa0</t>
+          <t>https://www.indeed.com/viewjob?jk=ec64dec814e44fc0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>First Legal</t>
+          <t>Ai Vantage</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, Prompt Engineering, CI/CD, Git, R, Java, Scala, Optimization</t>
+          <t>Docker, Kubernetes, Terraform, PostgreSQL, MySQL, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eccbf6b5fbbae8f0</t>
+          <t>https://www.indeed.com/viewjob?jk=87747bfcd30cdbc2</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>GTM Engineer, Hazel AI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>First Legal</t>
+          <t>ALTRUIST</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Henderson, NV, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, Prompt Engineering, CI/CD, Git, R, Java, Scala, Optimization</t>
+          <t>RAG, BigQuery, Snowflake, Databricks, BigQuery, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fed99ad6f10654d</t>
+          <t>https://www.indeed.com/viewjob?jk=6724f9993c022bc8</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Risk Management - AI/ML Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>First Legal</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Henderson, NV, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, Prompt Engineering, CI/CD, Git, R, Java, Scala, Optimization</t>
+          <t>LangChain, RAG, Docker, Kubernetes, Databricks, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d0b466949a1bdb1</t>
+          <t>https://www.indeed.com/viewjob?jk=123262b3b160f198</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Data Scientist/ Senior Data Scientist -Demand Forecasting</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>First Legal</t>
+          <t>Tiger Analytics</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Hollywood, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, Prompt Engineering, CI/CD, Git, R, Java, Scala, Optimization</t>
+          <t>Data Scientist, XGBoost, LightGBM, CatBoost, Databricks, PySpark, Python, R, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f4984cac15af1f8</t>
+          <t>https://www.indeed.com/viewjob?jk=e456131c0acdfa4e</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Data Scientist Senior Associate</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>First Legal</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, Prompt Engineering, CI/CD, Git, R, Java, Scala, Optimization</t>
+          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, Git, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,252 +776,42 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f7dd33c1c8dd9ef</t>
+          <t>https://www.indeed.com/viewjob?jk=6998765062eafc6a</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>CATIA Account Executive - Enterprise Software</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>First Legal</t>
+          <t>Dassault Systèmes</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, Prompt Engineering, CI/CD, Git, R, Java, Scala, Optimization</t>
+          <t>Generative AI, RAG, Prompt Engineering, CI/CD, Jenkins, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8b6a5f873843085</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Senior AI Engineer</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>First Legal</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Los Angeles, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>AI Engineer, LangChain, RAG, Prompt Engineering, CI/CD, Git, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bd445525a9885001</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Senior AI Engineer</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>First Legal</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Paris, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>AI Engineer, LangChain, RAG, Prompt Engineering, CI/CD, Git, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a8e2a2840837668d</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>GTM Engineer, Hazel AI</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>ALTRUIST</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>RAG, BigQuery, Snowflake, Databricks, BigQuery, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ace9e82efa6b4b13</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>GEN AI Engineer-1</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Realign</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Tampa, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>10</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>AI Engineer, LangChain, RAG, Prompt Engineering, Python, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f8c1f365e57c241d</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Marketing Analytics and Data Science Program Management Intern</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>AAA Life Insurance Company</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Livonia, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>10</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Data Scientist, Git, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=48646c7ec667696e</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Senior Product Software Engineer</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Wolters Kluwer</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>10</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>LangChain, RAG, TensorFlow, PyTorch, Git, Python, SQL, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f40684013e8a26dd</t>
+          <t>https://www.indeed.com/viewjob?jk=3970c133b965d57a</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-03-03.xlsx
+++ b/daily_matches/job_matches_2026-03-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Backend Software Engineer III - API Platform</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>police department</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, S3, Glue, Athena, Redshift, Docker, Kubernetes, Apache Airflow, Git, Snowflake</t>
+          <t>Data Scientist, RAG, PyTorch, NLTK, Git, Matplotlib, Python, SQL, R</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,322 +496,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd1c3ba542522bad</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>HCA Healthcare</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Nashville, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Dataflow, Kubernetes, CI/CD, Terraform, Git, Kafka, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a53eba2ddb1389c4</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Senior Software Developer, Platform Engineering</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Redfin</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R, Java</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=44e5ced55abe02e5</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Software Development Engineer III - AI Engineer</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Expedia Group</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Gemini, Pinecone, CI/CD, Kafka, NoSQL, SQL</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ec64dec814e44fc0</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Data Architect</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Ai Vantage</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Vienna, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Docker, Kubernetes, Terraform, PostgreSQL, MySQL, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=87747bfcd30cdbc2</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>GTM Engineer, Hazel AI</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>ALTRUIST</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>RAG, BigQuery, Snowflake, Databricks, BigQuery, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6724f9993c022bc8</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Risk Management - AI/ML Engineer</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>10</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>LangChain, RAG, Docker, Kubernetes, Databricks, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=123262b3b160f198</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Data Scientist/ Senior Data Scientist -Demand Forecasting</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Tiger Analytics</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>10</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Data Scientist, XGBoost, LightGBM, CatBoost, Databricks, PySpark, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e456131c0acdfa4e</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Data Scientist Senior Associate</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Wilmington, DE, US USA</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>10</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, Git, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6998765062eafc6a</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>CATIA Account Executive - Enterprise Software</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Dassault Systèmes</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>San Diego, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>10</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Prompt Engineering, CI/CD, Jenkins, Git, Python, R, Java</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3970c133b965d57a</t>
+          <t>https://www.indeed.com/viewjob?jk=daf707e59c91fd25</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-03-03.xlsx
+++ b/daily_matches/job_matches_2026-03-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,35 +468,455 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Data Engineer II (Hybrid Work Schedule)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>police department</t>
+          <t>Quorum Business Solutions</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Data Lake, Apache Airflow, CI/CD, Git, Snowflake, Databricks, PySpark, Python</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5f1e509811f28e16</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Software Engineering Intern</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>New York Post</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
           <t>New York, NY, US USA</t>
         </is>
       </c>
-      <c r="D2" t="n">
+      <c r="D3" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>RAG, S3, EC2, Glue, Athena, BigQuery, Kubernetes, Git, BigQuery, Python</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=97d6781b2e7b9433</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>AWS Network Engineer</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Generative AI, AWS SageMaker, EC2, Redshift, Kinesis, Docker, Kubernetes, CI/CD, Terraform, Redshift</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=571ca52ff80cfc56</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Entry Level Data Scientist - Collections Analytics</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Sequium Asset Solutions</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Data Scientist, XGBoost, LightGBM, Docker, Kubernetes, Git, Tableau, Power BI, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d64c7149195607e9</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Senior Frontend Engineer</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, S3, CI/CD, Git, Python, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a141527aeb823091</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Azure Network Engineer</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, Data Lake, MLflow, CI/CD, Databricks, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=662840de4364e997</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Azure Network Engineer</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, Data Lake, MLflow, CI/CD, Databricks, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7fc978b16714d0d2</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>AWS Network Engineer</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Hugging Face, PyTorch, S3, EC2, FastAPI, Docker, Kubernetes, CI/CD, Python, R</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a570b18450a89b20</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>LTIMindtree</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Git, PySpark, PostgreSQL, MySQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9649d08cb62a9ac0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Pansophic Learning</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Tysons, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>S3, EC2, Redshift, Git, Redshift, MongoDB, NoSQL, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=486581d09fdf7d49</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Google Cloud Network Engineer</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Docker, Kubernetes, Jenkins, GitHub Actions, Terraform, Git, Kafka, Python, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d128f0e1d0a3ad20</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026 Summer IT Intern, Cloud Engineering</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Eversource Energy</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>East Berlin, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
         <v>10</v>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, PyTorch, NLTK, Git, Matplotlib, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=daf707e59c91fd25</t>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>RAG, Synapse, Kubernetes, CI/CD, Terraform, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=559b54532dc39630</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>MTS 1, Software Engineer</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>eBay</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>10</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Git, MySQL, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=85d6d71b5c7b97c0</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-03-03.xlsx
+++ b/daily_matches/job_matches_2026-03-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Engineer II (Hybrid Work Schedule)</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Quorum Business Solutions</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>15.6</v>
+        <v>25.6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Data Lake, Apache Airflow, CI/CD, Git, Snowflake, Databricks, PySpark, Python</t>
+          <t>AI Engineer, Data Scientist, LangChain, RAG, LLaMA, Mistral, Hugging Face, FAISS, Pinecone, Prompt Engineering</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f1e509811f28e16</t>
+          <t>https://www.indeed.com/viewjob?jk=096d9e696ae3fadd</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Engineering Intern</t>
+          <t>Associate/Consultant Engineer - Remote</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>New York Post</t>
+          <t>Rancho BioSciences</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>13.3</v>
+        <v>18.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Glue, Athena, BigQuery, Kubernetes, Git, BigQuery, Python</t>
+          <t>RAG, Athena, Redshift, BigQuery, Docker, Kubernetes, CI/CD, Git, Snowflake, Databricks</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97d6781b2e7b9433</t>
+          <t>https://www.indeed.com/viewjob?jk=72630d316687619c</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Senior Software Engineer, Cloud Infrastructure</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>ALTRUIST</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.3</v>
+        <v>18.9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Generative AI, AWS SageMaker, EC2, Redshift, Kinesis, Docker, Kubernetes, CI/CD, Terraform, Redshift</t>
+          <t>Generative AI, RAG, Copilot, S3, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=571ca52ff80cfc56</t>
+          <t>https://www.indeed.com/viewjob?jk=cc6ad57eba624292</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Entry Level Data Scientist - Collections Analytics</t>
+          <t>Senior Software Engineer, Cloud Infrastructure</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Sequium Asset Solutions</t>
+          <t>ALTRUIST</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.3</v>
+        <v>18.9</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, XGBoost, LightGBM, Docker, Kubernetes, Git, Tableau, Power BI, Python, SQL</t>
+          <t>Generative AI, RAG, Copilot, S3, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d64c7149195607e9</t>
+          <t>https://www.indeed.com/viewjob?jk=15325ad687b27337</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Frontend Engineer</t>
+          <t>Senior AI Engineer, IT Solutions 1</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Celestica</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>NH, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12.2</v>
+        <v>18.9</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, S3, CI/CD, Git, Python, R, Java, Scala, Optimization</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Pinecone, Prompt Engineering, TensorFlow, PyTorch, MLflow</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a141527aeb823091</t>
+          <t>https://www.indeed.com/viewjob?jk=ee982b6d11792f00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Create Music Group</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12.2</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, Data Lake, MLflow, CI/CD, Databricks, Python, SQL, R</t>
+          <t>Data Scientist, Machine Learning Engineer, LangChain, RAG, Prompt Engineering, PyTorch, XGBoost, BigQuery, CI/CD, Git</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=662840de4364e997</t>
+          <t>https://www.indeed.com/viewjob?jk=d95184a32e9a727d</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Create Music Group</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12.2</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, Data Lake, MLflow, CI/CD, Databricks, Python, SQL, R</t>
+          <t>Data Scientist, Machine Learning Engineer, LangChain, RAG, Prompt Engineering, PyTorch, XGBoost, BigQuery, CI/CD, Git</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fc978b16714d0d2</t>
+          <t>https://www.indeed.com/viewjob?jk=9034c69b932f4fbe</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Data Engineer II (Hybrid Work Schedule)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Quorum Software</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.1</v>
+        <v>15.6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hugging Face, PyTorch, S3, EC2, FastAPI, Docker, Kubernetes, CI/CD, Python, R</t>
+          <t>Data Scientist, RAG, Data Lake, Apache Airflow, CI/CD, Git, Snowflake, Databricks, PySpark, Python</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a570b18450a89b20</t>
+          <t>https://www.indeed.com/viewjob?jk=76a633e7c45d5fa0</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Associate/Consultant Engineer - Remote</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Rancho BioSciences</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.1</v>
+        <v>15.6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Docker, Git, PySpark, PostgreSQL, MySQL, Python, SQL, R, Scala</t>
+          <t>RAG, Athena, Redshift, BigQuery, CI/CD, Git, Snowflake, Databricks, BigQuery, Redshift</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9649d08cb62a9ac0</t>
+          <t>https://www.indeed.com/viewjob?jk=cd467efc7d909226</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Pansophic Learning</t>
+          <t>Finastra</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tysons, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>S3, EC2, Redshift, Git, Redshift, MongoDB, NoSQL, SQL, R, Java</t>
+          <t>AI Engineer, LangChain, RAG, Copilot, FAISS, Pinecone, ChromaDB, Prompt Engineering, CI/CD, Git</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=486581d09fdf7d49</t>
+          <t>https://www.indeed.com/viewjob?jk=bca9c014b3eed159</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Google Cloud Network Engineer</t>
+          <t>Software Engineer, Data</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Acrisure LLC</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, Jenkins, GitHub Actions, Terraform, Git, Kafka, Python, R, Optimization</t>
+          <t>RAG, BigQuery, Data Lake, Dataflow, Apache Airflow, Databricks, BigQuery, Polars, Python, SQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,77 +846,1127 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d128f0e1d0a3ad20</t>
+          <t>https://www.indeed.com/viewjob?jk=2b12dfc8a5459a4f</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026 Summer IT Intern, Cloud Engineering</t>
+          <t>Agentic AI Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Eversource Energy</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>East Berlin, CT, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Synapse, Kubernetes, CI/CD, Terraform, Python, SQL, R, Scala</t>
+          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, Kubernetes, CI/CD, Jenkins, Terraform, R, Java</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=559b54532dc39630</t>
+          <t>https://www.indeed.com/viewjob?jk=f8a8bc7718a0bab3</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>MTS 1, Software Engineer</t>
+          <t>Engineer II, AI/ML</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>eBay</t>
+          <t>Loram</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Hugging Face, PyTorch, OpenCV, Docker, Kubernetes, CI/CD, Databricks, Python</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b46b19105268dc0f</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Engineer II, AI/ML</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Loram</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Georgetown, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Hugging Face, PyTorch, OpenCV, Docker, Kubernetes, CI/CD, Databricks, Python</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1fe78b37b8e5920d</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Engineer II, AI/ML</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Loram</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Hamel, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Hugging Face, PyTorch, OpenCV, Docker, Kubernetes, CI/CD, Databricks, Python</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e6744cab1d3f8a6e</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Analytics Forward Deployed Software Engineer 2</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Tampa General Hospital</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Data Scientist, Prompt Engineering, Data Lake, Git, PySpark, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=06eab8288ad15d6e</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>hatch IT</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>RAG, S3, EC2, Docker, CI/CD, Terraform, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b260e746e7b9c233</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Engineer II, AI/ML</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Loram</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Hamel, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Hugging Face, PyTorch, OpenCV, Docker, Kubernetes, CI/CD, Databricks, Python</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cae30946d80f8403</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Engineer AI and Machine Learning</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, LLaMA, Docker, Kubernetes, CI/CD, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ff74128156059217</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Senior AI Software Engineer</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>SentinelOne</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, MLflow, Docker, Kubernetes, Terraform, Databricks, NoSQL, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=80719f3d7f3804a4</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Level 3 (L3) DevOps Engineer (Mid-level)</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Knox Systems</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Docker, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=01ed1745dd6a602d</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>SRE/Incident Response</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Xbow</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8eaa457987a41e07</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>AI/ML Software Engineer</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>GE Aerospace</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NC, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, LangChain, RAG, Prompt Engineering, Docker, Kubernetes, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b545dc1fd40655a1</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Senior Risk Developer (Python/Azure)</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Sumitomo Group</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Data Lake, MLflow, CI/CD, Databricks, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7762d03304071b69</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Site Reliability Engineer (SRE)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>hatch IT</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, PostgreSQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c08c735142c13e1b</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Sr. Software Engineer - Risk Platform (Hybrid)</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>CrowdStrike</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Sunnyvale, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Copilot, Docker, Kubernetes, Git, Kafka, Cassandra, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=151fe9868f44f2f1</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Forward Deployed Engineer (FDE)</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>ISHIR</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=15ecc0cd2b5a2111</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Mid AI Engineer</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Management Science &amp; Innovation</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, TensorFlow, PyTorch, MLflow, Docker, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f7f5abcd895255c5</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Data Science Co-Op (NLP &amp; GenAI)</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Bose</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Framingham, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, LLaMA, Hugging Face, MLflow, Git, Snowflake, Databricks, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0d2ec51e79a14f6c</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Data Platform</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>PEARLY</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Santa Barbara, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>RAG, Docker, CI/CD, GitHub Actions, Terraform, Git, PostgreSQL, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=52fbd92226aade92</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Data Platform</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>PEARLY</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>RAG, Docker, CI/CD, GitHub Actions, Terraform, Git, PostgreSQL, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3e77317858ff838d</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Data Platform</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>PEARLY</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>RAG, Docker, CI/CD, GitHub Actions, Terraform, Git, PostgreSQL, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9737f288d965528f</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Senior Applied AI Engineer</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Bold</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Guaynabo, PR, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, LLaMA, CI/CD, Jenkins, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0de0e7b63c1b0a5e</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Spotify</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, Hugging Face, PyTorch, Python, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e156aab75b02d878</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Research Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>University of Rochester</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Rochester, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, Git, Python, SQL, R, Java, Julia, Scala</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=77067ce0e0215605</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Data Scientist - Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Lee Health</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Fort Myers, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
         <v>10</v>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>RAG, CI/CD, Git, MySQL, SQL, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=85d6d71b5c7b97c0</t>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4a24fc4266500d5f</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Data Engineer (Lakehouse &amp; Analytics Platform)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>TIC - The Industrial Company</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Lone Tree, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>10</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Data Lake, CI/CD, Git, Databricks, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=24ec01831b0ea6f2</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>DataVisor</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Mountain View, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>10</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>RAG, Kafka, Hadoop, Cassandra, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1342acb3cd645f87</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Software Engineer Consultant - Remote</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Allstate Insurance</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>10</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>RAG, S3, Docker, Kubernetes, CI/CD, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=369669cb1a2fe242</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Systems Analyst - Supply Chain</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Service Corporation International</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>10</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, RAG, TensorFlow, PyTorch, Power BI, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=875248ce5d7ad0b1</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Associate Software Engineer - .Net</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Tyler, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>10</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, CI/CD, Git, PostgreSQL, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=119c9422670757e7</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Senior Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Health Catalyst</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>10</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Terraform, Git, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=91e57f703c0d04b1</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Full Stack Developer (Back End Focus)</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Future Energy Enterprises LLC</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Berkeley, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>10</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>RAG, S3, Docker, CI/CD, GitHub Actions, Git, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c4dd1492699ad9c0</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-03-03.xlsx
+++ b/daily_matches/job_matches_2026-03-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G44"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Software Engineer II,</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>25.6</v>
+        <v>22.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, LangChain, RAG, LLaMA, Mistral, Hugging Face, FAISS, Pinecone, Prompt Engineering</t>
+          <t>Data Scientist, EC2, Redshift, Docker, Kubernetes, CI/CD, Terraform, Git, Snowflake, Databricks</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=096d9e696ae3fadd</t>
+          <t>https://www.indeed.com/viewjob?jk=28ab3491bb9f5589</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Associate/Consultant Engineer - Remote</t>
+          <t>Data Engineer - AI Practice Team</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Rancho BioSciences</t>
+          <t>American Bureau of Shipping (ABS)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.9</v>
+        <v>20</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Athena, Redshift, BigQuery, Docker, Kubernetes, CI/CD, Git, Snowflake, Databricks</t>
+          <t>RAG, S3, Glue, BigQuery, Synapse, Data Lake, Kinesis, CI/CD, Snowflake, Databricks</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72630d316687619c</t>
+          <t>https://www.indeed.com/viewjob?jk=98e9bc7cd1938bfd</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Cloud Infrastructure</t>
+          <t>Software Engineer in Test III - Data Analytics</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ALTRUIST</t>
+          <t>Emburse</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.9</v>
+        <v>20</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, S3, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
+          <t>Data Scientist, RAG, Redshift, BigQuery, CI/CD, Jenkins, GitHub Actions, Git, Snowflake, BigQuery</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc6ad57eba624292</t>
+          <t>https://www.indeed.com/viewjob?jk=450782bf82b6fc2f</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Cloud Infrastructure</t>
+          <t>AI Engineer/Architect-IFS Cloud</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ALTRUIST</t>
+          <t>Rockwell Automation</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, S3, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
+          <t>AI Engineer, Generative AI, RAG, Gemini, XGBoost, Azure ML, Docker, CI/CD, Terraform, PostgreSQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15325ad687b27337</t>
+          <t>https://www.indeed.com/viewjob?jk=0c154c59806de726</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior AI Engineer, IT Solutions 1</t>
+          <t>Identity AI / ML Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Celestica</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>NH, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.9</v>
+        <v>17.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Pinecone, Prompt Engineering, TensorFlow, PyTorch, MLflow</t>
+          <t>AI Engineer, Generative AI, RAG, LLaMA, Hugging Face, FAISS, Pinecone, ChromaDB, Prompt Engineering, TensorFlow</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee982b6d11792f00</t>
+          <t>https://www.indeed.com/viewjob?jk=7a259cfa68cdc834</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Junior AI Applications Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Create Music Group</t>
+          <t>Stanford University</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, LangChain, RAG, Prompt Engineering, PyTorch, XGBoost, BigQuery, CI/CD, Git</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Mistral, FAISS, Pinecone, Prompt Engineering, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d95184a32e9a727d</t>
+          <t>https://www.indeed.com/viewjob?jk=6d3bc7249bfcf9de</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Sr. Software Engineer, Computer Vision</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Create Music Group</t>
+          <t>SpaceX</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Hawthorne, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>15.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, LangChain, RAG, Prompt Engineering, PyTorch, XGBoost, BigQuery, CI/CD, Git</t>
+          <t>RAG, PyTorch, OpenCV, MLflow, Docker, Kubernetes, CI/CD, Kafka, PostgreSQL, Python</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9034c69b932f4fbe</t>
+          <t>https://www.indeed.com/viewjob?jk=7868dc32c6bb3231</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer II (Hybrid Work Schedule)</t>
+          <t>Software Engineer III - Data Engineering Java/Python</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Quorum Software</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Data Lake, Apache Airflow, CI/CD, Git, Snowflake, Databricks, PySpark, Python</t>
+          <t>RAG, Data Lake, CI/CD, Snowflake, Databricks, PySpark, Kafka, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76a633e7c45d5fa0</t>
+          <t>https://www.indeed.com/viewjob?jk=6dfc1c1ddf5b07e8</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Associate/Consultant Engineer - Remote</t>
+          <t>PDM Implementation Data Architect</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Rancho BioSciences</t>
+          <t>Availity, LLC.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Athena, Redshift, BigQuery, CI/CD, Git, Snowflake, Databricks, BigQuery, Redshift</t>
+          <t>RAG, S3, EC2, Glue, Athena, Redshift, Redshift, PySpark, MySQL, SQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd467efc7d909226</t>
+          <t>https://www.indeed.com/viewjob?jk=3576de9e88dd4c5c</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Finastra</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, Copilot, FAISS, Pinecone, ChromaDB, Prompt Engineering, CI/CD, Git</t>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Kafka</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bca9c014b3eed159</t>
+          <t>https://www.indeed.com/viewjob?jk=80460d4e824e28cc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Software Engineer, Data</t>
+          <t>Senior Data Scientist (Capital Markets)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Berkeley Heights, NJ, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Data Lake, Dataflow, Apache Airflow, Databricks, BigQuery, Polars, Python, SQL</t>
+          <t>Data Scientist, LangChain, RAG, LLaMA, TensorFlow, PyTorch, AWS SageMaker, Azure ML, Git, Snowflake</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b12dfc8a5459a4f</t>
+          <t>https://www.indeed.com/viewjob?jk=fee60b0a114cc0a6</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Agentic AI Engineer</t>
+          <t>Bioinformatics Software Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Memorial Sloan Kettering Cancer Center</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, Kubernetes, CI/CD, Jenkins, Terraform, R, Java</t>
+          <t>Data Scientist, RAG, Prompt Engineering, TensorFlow, PyTorch, FastAPI, MySQL, MongoDB, Python, SQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8a8bc7718a0bab3</t>
+          <t>https://www.indeed.com/viewjob?jk=05c13a624aa98f2e</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Engineer II, AI/ML</t>
+          <t>AI, Data &amp; Technology - AI-ML Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Loram</t>
+          <t>Grant Thornton</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Hugging Face, PyTorch, OpenCV, Docker, Kubernetes, CI/CD, Databricks, Python</t>
+          <t>RAG, TensorFlow, PyTorch, XGBoost, BigQuery, CI/CD, Snowflake, Databricks, BigQuery, Python</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b46b19105268dc0f</t>
+          <t>https://www.indeed.com/viewjob?jk=6017fc81a5dfe13c</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Engineer II, AI/ML</t>
+          <t>AI Scientist II (Healthcare)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Loram</t>
+          <t>Cambia Health Solutions</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Georgetown, TX, US USA</t>
+          <t>Renton, WA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Hugging Face, PyTorch, OpenCV, Docker, Kubernetes, CI/CD, Databricks, Python</t>
+          <t>Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, XGBoost, Python, SQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fe78b37b8e5920d</t>
+          <t>https://www.indeed.com/viewjob?jk=4d857191c0741c47</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Engineer II, AI/ML</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Loram</t>
+          <t>Surgery Partners</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Hamel, MN, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Hugging Face, PyTorch, OpenCV, Docker, Kubernetes, CI/CD, Databricks, Python</t>
+          <t>RAG, Synapse, Data Lake, MLflow, CI/CD, Git, Databricks, PySpark, SQL, R</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6744cab1d3f8a6e</t>
+          <t>https://www.indeed.com/viewjob?jk=17c87f0de0ddb952</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Analytics Forward Deployed Software Engineer 2</t>
+          <t>Software Engineer 2 - Analytics &amp; AI</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Tampa General Hospital</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Brookfield, WI, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Data Scientist, Prompt Engineering, Data Lake, Git, PySpark, Tableau, Power BI, Python, SQL, R</t>
+          <t>Synapse, Docker, Kubernetes, CI/CD, Git, Databricks, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06eab8288ad15d6e</t>
+          <t>https://www.indeed.com/viewjob?jk=75d602908669423e</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer 2 - Analytics &amp; AI</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hatch IT</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Docker, CI/CD, Terraform, Git, Python, R, Java</t>
+          <t>Synapse, Docker, Kubernetes, CI/CD, Git, Databricks, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b260e746e7b9c233</t>
+          <t>https://www.indeed.com/viewjob?jk=10de5f0ca2f7673d</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Engineer II, AI/ML</t>
+          <t>Software Engineer 2 - Analytics &amp; AI</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Loram</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Hamel, MN, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Hugging Face, PyTorch, OpenCV, Docker, Kubernetes, CI/CD, Databricks, Python</t>
+          <t>Synapse, Docker, Kubernetes, CI/CD, Git, Databricks, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cae30946d80f8403</t>
+          <t>https://www.indeed.com/viewjob?jk=8e6750fd9ad4e72e</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Engineer AI and Machine Learning</t>
+          <t>Software Engineer 2 - Analytics &amp; AI</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Cupertino, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, LLaMA, Docker, Kubernetes, CI/CD, Python, R, Java, Scala</t>
+          <t>Synapse, Docker, Kubernetes, CI/CD, Git, Databricks, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff74128156059217</t>
+          <t>https://www.indeed.com/viewjob?jk=c45db6ac50eb5587</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior AI Software Engineer</t>
+          <t>Software Engineer 2 - Analytics &amp; AI</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SentinelOne</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Gresham, OR, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, MLflow, Docker, Kubernetes, Terraform, Databricks, NoSQL, Python, SQL</t>
+          <t>Synapse, Docker, Kubernetes, CI/CD, Git, Databricks, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80719f3d7f3804a4</t>
+          <t>https://www.indeed.com/viewjob?jk=d1c0f7e27e90a87e</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Level 3 (L3) DevOps Engineer (Mid-level)</t>
+          <t>Software Engineer 2 - Analytics &amp; AI</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Knox Systems</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>Synapse, Docker, Kubernetes, CI/CD, Git, Databricks, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01ed1745dd6a602d</t>
+          <t>https://www.indeed.com/viewjob?jk=a4dc81e5cd9b6b72</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SRE/Incident Response</t>
+          <t>Software Engineer 2 - Analytics &amp; AI</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Xbow</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>Synapse, Docker, Kubernetes, CI/CD, Git, Databricks, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8eaa457987a41e07</t>
+          <t>https://www.indeed.com/viewjob?jk=14fea47c1dbfabac</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AI/ML Software Engineer</t>
+          <t>Software Engineer 2 - Analytics &amp; AI</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>GE Aerospace</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, LangChain, RAG, Prompt Engineering, Docker, Kubernetes, Git, Python, R</t>
+          <t>Synapse, Docker, Kubernetes, CI/CD, Git, Databricks, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b545dc1fd40655a1</t>
+          <t>https://www.indeed.com/viewjob?jk=02d7bcc2bd0697b0</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Risk Developer (Python/Azure)</t>
+          <t>Software Engineer 2 - Analytics &amp; AI</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Sumitomo Group</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Data Lake, MLflow, CI/CD, Databricks, Power BI, Python, SQL, R</t>
+          <t>Synapse, Docker, Kubernetes, CI/CD, Git, Databricks, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7762d03304071b69</t>
+          <t>https://www.indeed.com/viewjob?jk=50e0ff85e5f89851</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer (SRE)</t>
+          <t>Multi-Cloud Networking Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>hatch IT</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, PostgreSQL, Python, SQL, R, Java</t>
+          <t>Data Scientist, RAG, CI/CD, Git, Databricks, PySpark, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c08c735142c13e1b</t>
+          <t>https://www.indeed.com/viewjob?jk=cab7b07d708701fa</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - Risk Platform (Hybrid)</t>
+          <t>Senior Data Scientist - AI Practice Team</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>American Bureau of Shipping (ABS)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Copilot, Docker, Kubernetes, Git, Kafka, Cassandra, Python, SQL, R, Scala</t>
+          <t>Data Scientist, MLflow, Docker, CI/CD, Git, Databricks, Tableau, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,67 +1371,67 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=151fe9868f44f2f1</t>
+          <t>https://www.indeed.com/viewjob?jk=540f72e9dcda8dc2</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer (FDE)</t>
+          <t>DOCSIS Testing Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ISHIR</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Copilot, S3, EC2, Athena, CI/CD, Terraform, Git, Python, R</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15ecc0cd2b5a2111</t>
+          <t>https://www.indeed.com/viewjob?jk=15dc479023cc23ea</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Mid AI Engineer</t>
+          <t>DOCSIS Testing Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Management Science &amp; Innovation</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, TensorFlow, PyTorch, MLflow, Docker, Python, SQL, R, Scala</t>
+          <t>Redshift, Redshift, PostgreSQL, Tableau, Power BI, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7f5abcd895255c5</t>
+          <t>https://www.indeed.com/viewjob?jk=71135064bf9dd98c</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Science Co-Op (NLP &amp; GenAI)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Bose</t>
+          <t>Experity</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Framingham, MA, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Hugging Face, MLflow, Git, Snowflake, Databricks, Python, SQL</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,497 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d2ec51e79a14f6c</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - Data Platform</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>PEARLY</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Santa Barbara, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>RAG, Docker, CI/CD, GitHub Actions, Terraform, Git, PostgreSQL, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=52fbd92226aade92</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - Data Platform</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>PEARLY</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>RAG, Docker, CI/CD, GitHub Actions, Terraform, Git, PostgreSQL, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3e77317858ff838d</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - Data Platform</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>PEARLY</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>RAG, Docker, CI/CD, GitHub Actions, Terraform, Git, PostgreSQL, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9737f288d965528f</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Senior Applied AI Engineer</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Bold</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Guaynabo, PR, US USA</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, CI/CD, Jenkins, Git, Python, R, Java</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0de0e7b63c1b0a5e</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Spotify</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, Hugging Face, PyTorch, Python, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e156aab75b02d878</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Research Data Engineer II</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>University of Rochester</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Rochester, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, Git, Python, SQL, R, Java, Julia, Scala</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=77067ce0e0215605</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Data Scientist - Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Lee Health</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Fort Myers, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>10</v>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4a24fc4266500d5f</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Data Engineer (Lakehouse &amp; Analytics Platform)</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>TIC - The Industrial Company</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Lone Tree, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>10</v>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Data Lake, CI/CD, Git, Databricks, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=24ec01831b0ea6f2</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>DataVisor</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Mountain View, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>10</v>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>RAG, Kafka, Hadoop, Cassandra, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1342acb3cd645f87</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Software Engineer Consultant - Remote</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Allstate Insurance</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>10</v>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>RAG, S3, Docker, Kubernetes, CI/CD, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=369669cb1a2fe242</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Systems Analyst - Supply Chain</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Service Corporation International</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>10</v>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>AI Engineer, Machine Learning Engineer, RAG, TensorFlow, PyTorch, Power BI, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=875248ce5d7ad0b1</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Associate Software Engineer - .Net</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Ensora Health</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Tyler, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>10</v>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Docker, CI/CD, Git, PostgreSQL, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=119c9422670757e7</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Senior Cloud Engineer</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Health Catalyst</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D43" t="n">
-        <v>10</v>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>RAG, CI/CD, Terraform, Git, Databricks, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=91e57f703c0d04b1</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Full Stack Developer (Back End Focus)</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Future Energy Enterprises LLC</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Berkeley, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D44" t="n">
-        <v>10</v>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>RAG, S3, Docker, CI/CD, GitHub Actions, Git, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c4dd1492699ad9c0</t>
+          <t>https://www.indeed.com/viewjob?jk=ea23a423227fb6d9</t>
         </is>
       </c>
     </row>
